--- a/DATA/MASTER/C11_MASTER/Preparacion_Machine_Learning/ipm/variables_excluidas.xlsx
+++ b/DATA/MASTER/C11_MASTER/Preparacion_Machine_Learning/ipm/variables_excluidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,44 +486,44 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Puntaje_Redundancia</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Puntaje_Multicolinealidad</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Importancia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Puntaje_Conocimiento_Dominio</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>% Cobertura</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Puntaje_Calidad</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Puntaje_Redundancia</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Puntaje_Multicolinealidad</t>
-        </is>
-      </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>IPML</t>
@@ -537,16 +537,21 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Estado_Final</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Justificacion</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Temp_Max_C</t>
+          <t>SOLIDOS SUSPENDIDOS TOTALES</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -555,10 +560,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -567,57 +572,57 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>31.915</v>
+        <v>2.722</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
       </c>
       <c r="P2" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="R2" t="n">
-        <v>0.833</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>0.25</v>
+        <v>0.095</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7763</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -627,16 +632,21 @@
       <c r="V2" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Temp_Media_C</t>
+          <t>TEMPERATURA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -645,10 +655,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -657,57 +667,57 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>36.048</v>
+        <v>2.965</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="R3" t="n">
-        <v>0.833</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>0.25</v>
+        <v>0.095</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7763</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -717,16 +727,21 @@
       <c r="V3" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TEMPERATURA</t>
+          <t>TURBIDEZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -735,10 +750,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -747,11 +762,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.883</v>
+        <v>1.645</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -760,44 +775,44 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.667</v>
       </c>
-      <c r="P4" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.095</v>
-      </c>
       <c r="R4" t="n">
-        <v>0.833</v>
+        <v>6.44</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0.064</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7262</v>
+        <v>0.7732</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -807,16 +822,21 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SOLIDOS SUSPENDIDOS TOTALES</t>
+          <t>Anio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -825,10 +845,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -837,11 +857,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.705</v>
+        <v>4.188</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -850,44 +870,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.667</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
       </c>
       <c r="P5" t="n">
-        <v>9.470000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.095</v>
+        <v>0.333</v>
       </c>
       <c r="R5" t="n">
-        <v>0.833</v>
+        <v>100</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7262</v>
+        <v>0.7332</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -897,16 +917,21 @@
       <c r="V5" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TURBIDEZ</t>
+          <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -918,66 +943,66 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.619</v>
+        <v>6.742</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.667</v>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P6" t="n">
-        <v>6.44</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.064</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.833</v>
+        <v>18.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0.182</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7231</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -987,16 +1012,21 @@
       <c r="V6" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Anio</t>
+          <t>COBERTURA DE ALCANTARILLADO URBANO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1005,88 +1035,93 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5.779</v>
+        <v>3.032</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Temporal</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R7" t="n">
+        <v>100</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.7168</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P7" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.6832</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CONTINUIDAD DE ACUEDUCTO URBANO</t>
+          <t>ACCESO A AGUA POTABLE ADECUADO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1095,23 +1130,23 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2354914.55</v>
+        <v>37.091</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1120,63 +1155,68 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.667</v>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P8" t="n">
-        <v>18.18</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.182</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S8" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.635</v>
+        <v>0.7</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FOSFORO TOTAL</t>
+          <t>Temp_Max_C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1188,85 +1228,90 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>14.153</v>
+        <v>36.388</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.667</v>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P9" t="n">
-        <v>9.279999999999999</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.093</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.833</v>
+        <v>100</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.626</v>
+        <v>0.7</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NITROGENO TOTAL</t>
+          <t>Temp_Media_C</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1278,85 +1323,90 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10.296</v>
+        <v>82.34</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.667</v>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P10" t="n">
-        <v>5.49</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.055</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.833</v>
+        <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6222</v>
+        <v>0.7</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CONDUCTIVIDAD ELECTRICA</t>
+          <t>CONTINUIDAD DE ACUEDUCTO URBANO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1365,88 +1415,91 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Muy Baja</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>No Calculado</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>VIF no calculable por varianza nula de la variable.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Evaluar por separado debido a varianza nula; el VIF no es calculable.</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="Q11" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R11" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Baja redundancia estructural.</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>22.078</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P11" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.5264</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INDICE DE DESEMPENO INSTITUCIONAL</t>
+          <t>NITROGENO TOTAL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1455,88 +1508,93 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Muy Baja</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.434</v>
+        <v>10.278</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.6723</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Variable con baja dependencia estructural.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Institucional</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P12" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ACCESO A AGUA POTABLE ADECUADO</t>
+          <t>COBERTURA DE ALCANTARILLADO RURAL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1545,71 +1603,69 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>7.181</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
       </c>
       <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R13" t="n">
         <v>100</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -1619,16 +1675,21 @@
       <c r="V13" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+          <t>AGUAS RESIDUALES TRATADAS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1637,7 +1698,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -1649,59 +1710,57 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en el máximo relativo de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5.555</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>100</v>
-      </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5</v>
+        <v>0.5682</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1711,16 +1770,21 @@
       <c r="V14" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DENSIDAD POBLACIONAL</t>
+          <t>COBERTURA DE ACUEDUCTO RURAL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1729,71 +1793,69 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>32.439</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Demográfica</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>2</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.667</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>100</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3668</v>
+        <v>0.5668</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -1803,16 +1865,21 @@
       <c r="V15" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COBERTURA DE ACUEDUCTO RURAL</t>
+          <t>COBERTURA DE ACUEDUCTO URBANO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1821,71 +1888,69 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>42.952</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.667</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>100</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3668</v>
+        <v>0.5668</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -1895,16 +1960,21 @@
       <c r="V16" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COBERTURA DE ACUEDUCTO URBANO</t>
+          <t>DENSIDAD POBLACIONAL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1913,71 +1983,69 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1329.161</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Demográfica</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>2</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.667</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>100</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3668</v>
+        <v>0.5668</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -1987,16 +2055,21 @@
       <c r="V17" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COBERTURA DE ALCANTARILLADO RURAL</t>
+          <t>POBLACION TOTAL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2005,71 +2078,69 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1182.398</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Demográfica</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.667</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>100</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3668</v>
+        <v>0.5668</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2079,98 +2150,296 @@
       <c r="V18" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>33</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FOSFORO TOTAL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Numérica</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>14.559</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R19" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>34</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>COBERTURA DE ALCANTARILLADO URBANO</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CONDUCTIVIDAD ELECTRICA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Numérica</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>6</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>22.148</v>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N19" t="n">
+      <c r="P20" t="n">
         <v>2</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q20" t="n">
         <v>0.667</v>
       </c>
-      <c r="P19" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.4763</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>35</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>INDICE DE DESEMPENO INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Numérica</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Participa en el máximo relativo de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>8.381</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.3668</v>
-      </c>
-      <c r="U19" t="inlineStr">
+      <c r="M21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R21" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>No Prioritaria</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>IPML inferior al umbral definido.</t>
         </is>
       </c>
     </row>
